--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1604-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1604-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43C68AC-4D74-4DB1-8FB5-6CFEF8C1A30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A249F73A-B882-4F5D-BC6C-821D2BA16E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B7B2E145-125C-4326-9526-5977B694D08E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E04B11AE-439A-4EF9-92F6-9F1450530488}"/>
   </bookViews>
   <sheets>
     <sheet name="1604-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1571,29 +1571,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC8792EA-043F-4039-960B-3EDDE695C69E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5240ADB6-6264-4142-BB48-8DBAAADE9831}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1626,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1662,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1714,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1783,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1855,7 +1854,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1927,7 +1926,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1999,7 +1998,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2143,7 +2142,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2215,7 +2214,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2287,7 +2286,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2359,7 +2358,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2431,7 +2430,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2503,7 +2502,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2575,7 +2574,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2647,7 +2646,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2719,7 +2718,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2791,7 +2790,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2863,7 +2862,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2935,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3007,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3079,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3151,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3223,7 +3222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3295,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2003</v>
       </c>
@@ -3367,7 +3366,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="43"/>
       <c r="B27" s="44"/>
       <c r="C27" s="18" t="s">
@@ -3395,7 +3394,7 @@
       <c r="W27" s="52"/>
       <c r="X27" s="46"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2002</v>
       </c>
@@ -3467,7 +3466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2001</v>
       </c>
@@ -3539,7 +3538,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1999</v>
       </c>
@@ -3683,7 +3682,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3755,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1997</v>
       </c>
@@ -3827,7 +3826,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1996</v>
       </c>
@@ -3899,7 +3898,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1995</v>
       </c>
@@ -3971,7 +3970,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>1994</v>
       </c>
@@ -4043,7 +4042,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="55"/>
       <c r="B37" s="56"/>
       <c r="C37" s="20" t="s">
@@ -4071,7 +4070,7 @@
       <c r="W37" s="62"/>
       <c r="X37" s="58"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1993</v>
       </c>
@@ -4143,7 +4142,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="43"/>
       <c r="B39" s="44"/>
       <c r="C39" s="18" t="s">
@@ -4171,7 +4170,7 @@
       <c r="W39" s="52"/>
       <c r="X39" s="46"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1992</v>
       </c>
@@ -4243,7 +4242,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="41">
         <v>1991</v>
       </c>
@@ -4315,7 +4314,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="43"/>
       <c r="B42" s="44"/>
       <c r="C42" s="18" t="s">
@@ -4343,7 +4342,7 @@
       <c r="W42" s="52"/>
       <c r="X42" s="46"/>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1990</v>
       </c>
@@ -4415,7 +4414,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>1989</v>
       </c>
@@ -4487,7 +4486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1988</v>
       </c>
@@ -4559,7 +4558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>1987</v>
       </c>
@@ -4631,7 +4630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1986</v>
       </c>
@@ -4703,7 +4702,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1985</v>
       </c>
@@ -4775,7 +4774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1984</v>
       </c>
@@ -4847,7 +4846,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>1983</v>
       </c>
@@ -4919,7 +4918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37" t="s">
         <v>57</v>
       </c>
